--- a/data/nzd0187/nzd0187.xlsx
+++ b/data/nzd0187/nzd0187.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G439"/>
+  <dimension ref="A1:G446"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12229,6 +12229,195 @@
         <v>419.52</v>
       </c>
       <c r="G439" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:11:43+00:00</t>
+        </is>
+      </c>
+      <c r="B440" t="n">
+        <v>417.3</v>
+      </c>
+      <c r="C440" t="n">
+        <v>428.08</v>
+      </c>
+      <c r="D440" t="n">
+        <v>428.66</v>
+      </c>
+      <c r="E440" t="n">
+        <v>427.18</v>
+      </c>
+      <c r="F440" t="n">
+        <v>420.48</v>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:05:26+00:00</t>
+        </is>
+      </c>
+      <c r="B441" t="n">
+        <v>416.57</v>
+      </c>
+      <c r="C441" t="n">
+        <v>426.8</v>
+      </c>
+      <c r="D441" t="n">
+        <v>428.15</v>
+      </c>
+      <c r="E441" t="n">
+        <v>426.86</v>
+      </c>
+      <c r="F441" t="n">
+        <v>420.02</v>
+      </c>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B442" t="n">
+        <v>415.44</v>
+      </c>
+      <c r="C442" t="n">
+        <v>427.31</v>
+      </c>
+      <c r="D442" t="n">
+        <v>428.38</v>
+      </c>
+      <c r="E442" t="n">
+        <v>427.71</v>
+      </c>
+      <c r="F442" t="n">
+        <v>420.09</v>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B443" t="n">
+        <v>415.44</v>
+      </c>
+      <c r="C443" t="n">
+        <v>427.57</v>
+      </c>
+      <c r="D443" t="n">
+        <v>428.45</v>
+      </c>
+      <c r="E443" t="n">
+        <v>427.89</v>
+      </c>
+      <c r="F443" t="n">
+        <v>419.36</v>
+      </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:11:53+00:00</t>
+        </is>
+      </c>
+      <c r="B444" t="n">
+        <v>414.78</v>
+      </c>
+      <c r="C444" t="n">
+        <v>425.68</v>
+      </c>
+      <c r="D444" t="n">
+        <v>427.9</v>
+      </c>
+      <c r="E444" t="n">
+        <v>426.78</v>
+      </c>
+      <c r="F444" t="n">
+        <v>419.71</v>
+      </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:05:32+00:00</t>
+        </is>
+      </c>
+      <c r="B445" t="n">
+        <v>414.06</v>
+      </c>
+      <c r="C445" t="n">
+        <v>424.48</v>
+      </c>
+      <c r="D445" t="n">
+        <v>426.84</v>
+      </c>
+      <c r="E445" t="n">
+        <v>426.05</v>
+      </c>
+      <c r="F445" t="n">
+        <v>419.58</v>
+      </c>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:48+00:00</t>
+        </is>
+      </c>
+      <c r="B446" t="n">
+        <v>414.06</v>
+      </c>
+      <c r="C446" t="n">
+        <v>425.08</v>
+      </c>
+      <c r="D446" t="n">
+        <v>427.01</v>
+      </c>
+      <c r="E446" t="n">
+        <v>426.42</v>
+      </c>
+      <c r="F446" t="n">
+        <v>420.29</v>
+      </c>
+      <c r="G446" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -12245,7 +12434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B588"/>
+  <dimension ref="A1:B595"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18128,6 +18317,76 @@
       </c>
       <c r="B588" t="n">
         <v>0.16</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B589" t="n">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B590" t="n">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B591" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B592" t="n">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B593" t="n">
+        <v>-0.39</v>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B594" t="n">
+        <v>-0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B595" t="n">
+        <v>0.92</v>
       </c>
     </row>
   </sheetData>
@@ -18296,28 +18555,28 @@
         <v>0.0347</v>
       </c>
       <c r="I2" t="n">
-        <v>6.445491519882997</v>
+        <v>6.408948730281782</v>
       </c>
       <c r="J2" t="n">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="K2" t="n">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="L2" t="n">
-        <v>0.802647921605079</v>
+        <v>0.8047268397418026</v>
       </c>
       <c r="M2" t="n">
-        <v>14.57343854506646</v>
+        <v>14.58198046395885</v>
       </c>
       <c r="N2" t="n">
-        <v>574.924932441619</v>
+        <v>568.3580752993738</v>
       </c>
       <c r="O2" t="n">
-        <v>23.97759229867793</v>
+        <v>23.8402616449437</v>
       </c>
       <c r="P2" t="n">
-        <v>255.6675826565939</v>
+        <v>256.0721553122897</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -18378,28 +18637,28 @@
         <v>0.0289</v>
       </c>
       <c r="I3" t="n">
-        <v>6.360586848151138</v>
+        <v>6.357556781020818</v>
       </c>
       <c r="J3" t="n">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="K3" t="n">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7394664410460043</v>
+        <v>0.7448703148737518</v>
       </c>
       <c r="M3" t="n">
-        <v>17.13569555527978</v>
+        <v>16.89016169937434</v>
       </c>
       <c r="N3" t="n">
-        <v>797.3615290375578</v>
+        <v>784.7527548109414</v>
       </c>
       <c r="O3" t="n">
-        <v>28.23759070879734</v>
+        <v>28.01343882515928</v>
       </c>
       <c r="P3" t="n">
-        <v>257.0711386705448</v>
+        <v>257.1048078556022</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -18460,28 +18719,28 @@
         <v>0.0363</v>
       </c>
       <c r="I4" t="n">
-        <v>5.990385497337986</v>
+        <v>5.992824449855942</v>
       </c>
       <c r="J4" t="n">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="K4" t="n">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8753510768523062</v>
+        <v>0.878580016091222</v>
       </c>
       <c r="M4" t="n">
-        <v>11.49738900312582</v>
+        <v>11.32991216675027</v>
       </c>
       <c r="N4" t="n">
-        <v>286.8343533075252</v>
+        <v>282.3026221085786</v>
       </c>
       <c r="O4" t="n">
-        <v>16.93618473291801</v>
+        <v>16.80186364986273</v>
       </c>
       <c r="P4" t="n">
-        <v>266.5323361935725</v>
+        <v>266.5053474727657</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -18542,28 +18801,28 @@
         <v>0.0335</v>
       </c>
       <c r="I5" t="n">
-        <v>5.365550161647275</v>
+        <v>5.367295906949032</v>
       </c>
       <c r="J5" t="n">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="K5" t="n">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8812715823973031</v>
+        <v>0.8843479588896003</v>
       </c>
       <c r="M5" t="n">
-        <v>11.40081371340598</v>
+        <v>11.23330453083504</v>
       </c>
       <c r="N5" t="n">
-        <v>218.3070005597156</v>
+        <v>214.8552091364205</v>
       </c>
       <c r="O5" t="n">
-        <v>14.77521575340663</v>
+        <v>14.65794013961104</v>
       </c>
       <c r="P5" t="n">
-        <v>282.5924976519944</v>
+        <v>282.5732099450428</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -18624,28 +18883,28 @@
         <v>0.0432</v>
       </c>
       <c r="I6" t="n">
-        <v>5.206688899607859</v>
+        <v>5.194779010014782</v>
       </c>
       <c r="J6" t="n">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="K6" t="n">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8708037965797921</v>
+        <v>0.8733881488993904</v>
       </c>
       <c r="M6" t="n">
-        <v>11.66079251503455</v>
+        <v>11.53586320831363</v>
       </c>
       <c r="N6" t="n">
-        <v>224.9831295132049</v>
+        <v>221.6218131317247</v>
       </c>
       <c r="O6" t="n">
-        <v>14.99943763989853</v>
+        <v>14.88696789583845</v>
       </c>
       <c r="P6" t="n">
-        <v>284.6237942840613</v>
+        <v>284.7567339429755</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -18687,7 +18946,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G439"/>
+  <dimension ref="A1:G446"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34813,6 +35072,265 @@
         </is>
       </c>
     </row>
+    <row r="440">
+      <c r="A440" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:11:43+00:00</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>-36.98026485094144,174.4686204015815</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>-36.979589102586786,174.4682982941849</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>-36.978891552589424,174.46808750370454</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>-36.9781895944775,174.46789919438413</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>-36.97747647625684,174.46776785081403</t>
+        </is>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:05:26+00:00</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>-36.98026329108426,174.46862836837002</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>-36.97958636752558,174.46831226323545</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>-36.97889046284593,174.46809306945002</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>-36.97818891072082,174.46790268658594</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>-36.977475493359805,174.46777287080846</t>
+        </is>
+      </c>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>-36.98026087650979,174.46864070052143</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>-36.97958745727673,174.46830669744202</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>-36.97889095429891,174.46809055940795</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>-36.9781907269493,174.46789341042475</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>-36.977475642931104,174.46777210689626</t>
+        </is>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>-36.98026087650979,174.46864070052143</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>-36.97958801283603,174.46830385997862</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>-36.97889110387155,174.46808979548211</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>-36.97819111156228,174.46789144606117</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>-36.97747408311586,174.46778007340893</t>
+        </is>
+      </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:11:53+00:00</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>-36.98025946622678,174.46864790337054</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>-36.97958397434569,174.46832448615385</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>-36.97888992865785,174.46809579775655</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>-36.97818873978163,174.46790355963637</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>-36.977474830972554,174.46777625384811</t>
+        </is>
+      </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:05:32+00:00</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>-36.98025792773571,174.4686557610238</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>-36.979581410223,174.4683375821369</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>-36.9788876636997,174.4681073657759</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>-36.978187179961246,174.46791152622146</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>-36.977474553197226,174.46777767254213</t>
+        </is>
+      </c>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:48+00:00</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>-36.98025792773571,174.4686557610238</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>-36.979582692284524,174.4683310341455</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>-36.97888802694779,174.46810551052755</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>-36.978187970555204,174.46790748836332</t>
+        </is>
+      </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>-36.97747607027765,174.46776992429</t>
+        </is>
+      </c>
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0187/nzd0187.xlsx
+++ b/data/nzd0187/nzd0187.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G446"/>
+  <dimension ref="A1:G448"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12418,6 +12418,60 @@
         <v>420.29</v>
       </c>
       <c r="G446" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:40+00:00</t>
+        </is>
+      </c>
+      <c r="B447" t="n">
+        <v>414.46</v>
+      </c>
+      <c r="C447" t="n">
+        <v>425.15</v>
+      </c>
+      <c r="D447" t="n">
+        <v>427.03</v>
+      </c>
+      <c r="E447" t="n">
+        <v>426.44</v>
+      </c>
+      <c r="F447" t="n">
+        <v>420.83</v>
+      </c>
+      <c r="G447" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B448" t="n">
+        <v>412.32</v>
+      </c>
+      <c r="C448" t="n">
+        <v>422.78</v>
+      </c>
+      <c r="D448" t="n">
+        <v>425.31</v>
+      </c>
+      <c r="E448" t="n">
+        <v>425.12</v>
+      </c>
+      <c r="F448" t="n">
+        <v>420.17</v>
+      </c>
+      <c r="G448" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -12434,7 +12488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B595"/>
+  <dimension ref="A1:B597"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18387,6 +18441,26 @@
       </c>
       <c r="B595" t="n">
         <v>0.92</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B596" t="n">
+        <v>-0.75</v>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B597" t="n">
+        <v>-0.7</v>
       </c>
     </row>
   </sheetData>
@@ -18555,28 +18629,28 @@
         <v>0.0347</v>
       </c>
       <c r="I2" t="n">
-        <v>6.408948730281782</v>
+        <v>6.397011253836098</v>
       </c>
       <c r="J2" t="n">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="K2" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8047268397418026</v>
+        <v>0.8051398571558794</v>
       </c>
       <c r="M2" t="n">
-        <v>14.58198046395885</v>
+        <v>14.59705773641771</v>
       </c>
       <c r="N2" t="n">
-        <v>568.3580752993738</v>
+        <v>566.7853181684178</v>
       </c>
       <c r="O2" t="n">
-        <v>23.8402616449437</v>
+        <v>23.80725347805618</v>
       </c>
       <c r="P2" t="n">
-        <v>256.0721553122897</v>
+        <v>256.204856524106</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -18637,28 +18711,28 @@
         <v>0.0289</v>
       </c>
       <c r="I3" t="n">
-        <v>6.357556781020818</v>
+        <v>6.354344384218661</v>
       </c>
       <c r="J3" t="n">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="K3" t="n">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7448703148737518</v>
+        <v>0.7462087124323129</v>
       </c>
       <c r="M3" t="n">
-        <v>16.89016169937434</v>
+        <v>16.83754352487611</v>
       </c>
       <c r="N3" t="n">
-        <v>784.7527548109414</v>
+        <v>781.28913506552</v>
       </c>
       <c r="O3" t="n">
-        <v>28.01343882515928</v>
+        <v>27.95154977931492</v>
       </c>
       <c r="P3" t="n">
-        <v>257.1048078556022</v>
+        <v>257.1406142750225</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -18719,28 +18793,28 @@
         <v>0.0363</v>
       </c>
       <c r="I4" t="n">
-        <v>5.992824449855942</v>
+        <v>5.991705785311816</v>
       </c>
       <c r="J4" t="n">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="K4" t="n">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="L4" t="n">
-        <v>0.878580016091222</v>
+        <v>0.8794021372958538</v>
       </c>
       <c r="M4" t="n">
-        <v>11.32991216675027</v>
+        <v>11.28562546007064</v>
       </c>
       <c r="N4" t="n">
-        <v>282.3026221085786</v>
+        <v>281.0411824623718</v>
       </c>
       <c r="O4" t="n">
-        <v>16.80186364986273</v>
+        <v>16.76428293910514</v>
       </c>
       <c r="P4" t="n">
-        <v>266.5053474727657</v>
+        <v>266.5177971705974</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -18801,28 +18875,28 @@
         <v>0.0335</v>
       </c>
       <c r="I5" t="n">
-        <v>5.367295906949032</v>
+        <v>5.366457396794878</v>
       </c>
       <c r="J5" t="n">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="K5" t="n">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8843479588896003</v>
+        <v>0.885142333699696</v>
       </c>
       <c r="M5" t="n">
-        <v>11.23330453083504</v>
+        <v>11.18676401985973</v>
       </c>
       <c r="N5" t="n">
-        <v>214.8552091364205</v>
+        <v>213.8927971725725</v>
       </c>
       <c r="O5" t="n">
-        <v>14.65794013961104</v>
+        <v>14.62507426212163</v>
       </c>
       <c r="P5" t="n">
-        <v>282.5732099450428</v>
+        <v>282.5825269727428</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -18883,28 +18957,28 @@
         <v>0.0432</v>
       </c>
       <c r="I6" t="n">
-        <v>5.194779010014782</v>
+        <v>5.19166096903156</v>
       </c>
       <c r="J6" t="n">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="K6" t="n">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8733881488993904</v>
+        <v>0.8741142009888394</v>
       </c>
       <c r="M6" t="n">
-        <v>11.53586320831363</v>
+        <v>11.49931115499376</v>
       </c>
       <c r="N6" t="n">
-        <v>221.6218131317247</v>
+        <v>220.6717136449532</v>
       </c>
       <c r="O6" t="n">
-        <v>14.88696789583845</v>
+        <v>14.85502317887634</v>
       </c>
       <c r="P6" t="n">
-        <v>284.7567339429755</v>
+        <v>284.7916844550191</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -18946,7 +19020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G446"/>
+  <dimension ref="A1:G448"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35331,6 +35405,80 @@
         </is>
       </c>
     </row>
+    <row r="447">
+      <c r="A447" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:40+00:00</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>-36.980258782453035,174.4686513956609</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>-36.97958284185835,174.46833027021313</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>-36.97888806968286,174.46810529226306</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>-36.97818801329001,174.4679072701007</t>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>-36.977477224113144,174.46776403125298</t>
+        </is>
+      </c>
+      <c r="G447" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>-36.98025420971353,174.46867475035114</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>-36.979577777713416,174.46835613477802</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>-36.9788843944657,174.46812406301004</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>-36.978185192792054,174.46792167543208</t>
+        </is>
+      </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>-36.97747581386973,174.46777123385377</t>
+        </is>
+      </c>
+      <c r="G448" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
